--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
